--- a/QA Test cases xlsx.xlsx
+++ b/QA Test cases xlsx.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUSL\Chat_Bot-Test\QA-Manual portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SUSL\Chat_Bot-Test\QA-Manual portfolio\QA-Manual-Testing-Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF736D67-F6E3-4156-969D-10668A1EE0FA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C63D3B9-64A2-4B88-AD0E-40583C86DA14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Test Case Template for Project</t>
   </si>
@@ -93,6 +93,27 @@
   <si>
     <t>3.Click the sign in button</t>
   </si>
+  <si>
+    <t>https://www.facebook.com page is loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login Scenario with Valid User </t>
+  </si>
+  <si>
+    <t>Login should work with valid CREDENTIALS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login is working with </t>
+  </si>
+  <si>
+    <t>valid credentials</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Buddhi</t>
+  </si>
 </sst>
 </file>
 
@@ -132,7 +153,7 @@
       <name val="Lato"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -160,6 +181,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor rgb="FFF3F3F3"/>
       </patternFill>
     </fill>
@@ -205,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -219,10 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -232,6 +255,23 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -463,16 +503,19 @@
     <col min="3" max="3" width="33.44140625" customWidth="1"/>
     <col min="4" max="4" width="31.21875" customWidth="1"/>
     <col min="5" max="5" width="62" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
     <col min="7" max="7" width="21.77734375" customWidth="1"/>
+    <col min="9" max="9" width="24.21875" customWidth="1"/>
+    <col min="10" max="10" width="25.109375" customWidth="1"/>
+    <col min="11" max="11" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12"/>
+      <c r="C1" s="16"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
@@ -602,7 +645,7 @@
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="11">
         <v>46188</v>
       </c>
       <c r="D5" s="1"/>
@@ -692,7 +735,7 @@
       <c r="Z7" s="1"/>
       <c r="AA7" s="1"/>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" ht="13.2">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -721,7 +764,7 @@
       <c r="Z8" s="7"/>
       <c r="AA8" s="7"/>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" ht="13.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -801,49 +844,65 @@
       <c r="Z10" s="9"/>
       <c r="AA10" s="9"/>
     </row>
-    <row r="11" spans="1:27" s="15" customFormat="1" ht="12" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="16" t="s">
+    <row r="11" spans="1:27" s="13" customFormat="1" ht="12" customHeight="1">
+      <c r="A11" s="19">
+        <v>1</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14"/>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="14"/>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="14"/>
-      <c r="Y11" s="14"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
+      <c r="F11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="12"/>
+      <c r="R11" s="12"/>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="12"/>
+      <c r="X11" s="12"/>
+      <c r="Y11" s="12"/>
+      <c r="Z11" s="12"/>
+      <c r="AA11" s="12"/>
     </row>
     <row r="12" spans="1:27" ht="13.2">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="A12" s="19"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="20"/>
       <c r="E12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="10"/>
+      <c r="F12" s="20"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="18"/>
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
@@ -863,18 +922,20 @@
       <c r="Z12" s="10"/>
       <c r="AA12" s="10"/>
     </row>
-    <row r="13" spans="1:27">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
+    <row r="13" spans="1:27" ht="13.2">
+      <c r="A13" s="19"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="20"/>
       <c r="E13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="21"/>
+      <c r="I13" s="18"/>
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -894,16 +955,16 @@
       <c r="Z13" s="7"/>
       <c r="AA13" s="7"/>
     </row>
-    <row r="14" spans="1:27">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10"/>
+    <row r="14" spans="1:27" ht="13.2">
+      <c r="A14" s="19"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="18"/>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
@@ -923,7 +984,7 @@
       <c r="Z14" s="10"/>
       <c r="AA14" s="10"/>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" ht="13.2">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -952,7 +1013,7 @@
       <c r="Z15" s="7"/>
       <c r="AA15" s="7"/>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" ht="13.2">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -981,7 +1042,7 @@
       <c r="Z16" s="10"/>
       <c r="AA16" s="10"/>
     </row>
-    <row r="17" spans="1:27">
+    <row r="17" spans="1:27" ht="13.2">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -29547,8 +29608,15 @@
       <c r="AA1001" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="8">
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="H11:H13"/>
     <mergeCell ref="B1:C1"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="B11:B14"/>
+    <mergeCell ref="A11:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
